--- a/erp_WB_test.xlsx
+++ b/erp_WB_test.xlsx
@@ -3499,7 +3499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3566,6 +3566,42 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>失败重试</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>pytest-rerunfailures；pytestmark = pytest.mark.flaky(reruns=2, reruns_delay=3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>日志</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>utils/logger.py；reports/logs/erp_wb.log；关弹窗打 WARNING</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>兜底关弹窗</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>BasePage.dismiss_popups() 在点击/填表/跳转前调用；无弹窗不报错；toast() 前不调用</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/erp_WB_test.xlsx
+++ b/erp_WB_test.xlsx
@@ -3499,7 +3499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3602,6 +3602,138 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>刊登页判定</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>仅 URL 含 wb-one-click-listing 视为刊登编辑页；拉取成功须出现 offerId+一键刊登，不能把 toast 当成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Allure</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>pytest 写入 reports/allure-results；浏览器查看：allure serve reports/allure-results（不要直接看 JSON）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>模块路径</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>商品 &gt; 商品采集 / 商品 &gt; WB商品刊登</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1688链接</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://detail.1688.com/offer/726638874254.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>入口对照</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>手动采集-1688商品链接采集；1688精选 tab=pallet；京东精选 tab=jd-pallet；淘宝精选 tab=taobao-pallet</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>刊登页必填（红色*）</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>上架店铺、选择仓库、产品类目、包装重量kg、包装尺寸cm、变体俄罗斯尺码*</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>标题规则</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>中文标题与俄语标题二选一；上限各60字；都为空提交失败</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>库存规则</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>库存不得超过100000；涉及库存上传须先拉取并选择WB仓库</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Club折扣</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0 或 3-31，失焦自动修正</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>草稿校验</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>含标题、类目、库存与 attrJson 合法 JSON；仅「可刊登」可批量提交</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>当前环境备注</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1688精选、淘宝精选列表为空；京东精选有数据；1688链接726638874254可拉取成功</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/erp_WB_test.xlsx
+++ b/erp_WB_test.xlsx
@@ -1196,12 +1196,12 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>勾选至少1条，目标店铺选择[WILDBERRIES]店铺，点击「批量生成草稿」</t>
+          <t>勾选1条，目标店铺选 WB 店铺，点「批量生成草稿」，确认框点确定</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>在WB商品刊登草稿箱生成对应草稿，来源可追溯1688精选；点「编辑」进入草稿页后产品类目仍为推荐预填</t>
+          <t>草稿箱条数增加或出现来源「1688精选」；点该行「编辑」后产品类目仍为推荐预填</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>有货时执行</t>
+          <t>有货时执行；不要只断言页面有「草稿」二字</t>
         </is>
       </c>
     </row>
@@ -1600,12 +1600,12 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>本页全选或勾选若干条，目标店铺选[WB]天津智云，点「批量生成草稿」</t>
+          <t>勾选1条，目标店铺选[WB]天津智云，点「批量生成草稿」，确认框点确定</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>草稿箱新增对应条数，来源为京东精选；编辑草稿页产品类目为推荐预填</t>
+          <t>草稿箱来源列出现「京东精选」（不能只看已有1688草稿）；点该行「编辑」后产品类目为推荐预填</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1613,7 +1613,11 @@
           <t>待执行</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr"/>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>有货时执行</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="48" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
@@ -1848,12 +1852,12 @@
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>勾选商品并选择WB目标店铺后「批量生成草稿」</t>
+          <t>勾选1条并选择WB目标店铺后「批量生成草稿」，确认框点确定</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>草稿箱生成对应草稿，来源可追溯淘宝精选；编辑草稿页产品类目为推荐预填</t>
+          <t>草稿箱来源列出现「淘宝精选」（不能只看已有1688草稿）；点该行「编辑」后产品类目为推荐预填</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -3499,7 +3503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3734,6 +3738,18 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>批量草稿来源</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TC13/21/26 须在草稿箱核对来源列（1688精选/京东精选/淘宝精选）；确认框点确定，勿点取消</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/erp_WB_test.xlsx
+++ b/erp_WB_test.xlsx
@@ -1715,7 +1715,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>当前环境实测为空</t>
+          <t>有卡片商品（含一键刊登/offerId）时跳过空列表断言</t>
         </is>
       </c>
     </row>
@@ -3503,7 +3503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3750,6 +3750,18 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>精选卡片有货</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1688/淘宝精选为卡片：有货认一键刊登下拉或 offerId：数字；勾选卡片复选框，不要只找表格 button</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/erp_WB_test.xlsx
+++ b/erp_WB_test.xlsx
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3491,6 +3491,206 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>WB商品刊登-包装带出</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>账号luojiaxing1已登录如斯达ERP，1688链接采集已拉取 offer 726638874254</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>带出/包装重量尺寸</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>先读卡片/查看详情中的原商品包装，再一键刊登 WB，核对刊登页重量与长宽高</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>与原商品一致：样例为 0.8kg、42×32×5cm；货源无对应项则刊登页该项为空</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>test_tc59</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>WB商品刊登-包装带出</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>账号luojiaxing1已登录如斯达ERP，1688精选有可售商品</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>带出/包装重量尺寸</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>先读该条原商品包装，再一键刊登 WB，核对刊登页</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>重量/长宽高与原商品一致；原商品没有的项刊登页留空；无货跳过</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>test_tc60</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>WB商品刊登-包装带出</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>账号luojiaxing1已登录如斯达ERP，京东精选有可售商品</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>带出/包装重量尺寸</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>先读该条原商品包装，再一键刊登 WB，核对刊登页</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>重量/长宽高与原商品一致；原商品没有的项刊登页留空；无货跳过</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>test_tc61</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>WB商品刊登-包装带出</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>账号luojiaxing1已登录如斯达ERP，淘宝精选有可售商品</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>带出/包装重量尺寸</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>先读该条原商品包装，再一键刊登 WB，核对刊登页</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>重量/长宽高与原商品一致；原商品没有的项刊登页留空；无货跳过</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>test_tc62</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3503,7 +3703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3762,6 +3962,18 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>包装带出</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>包装带出须与原商品一致：卡片/查看详情有值则刊登页相等；没有则留空。TC59 样例 0.8kg 42x32x5。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/erp_WB_test.xlsx
+++ b/erp_WB_test.xlsx
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:J71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>入口/空列表</t>
+          <t>入口/空或有货</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>展示「暂无1688精选商品」，共0条；不出现可点的一键刊登商品卡</t>
+          <t>无货展示暂无1688精选商品；有货则出现一键刊登卡片</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>当前环境实测为空列表</t>
+          <t>两种环境都执行分支断言</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>勾选1条，目标店铺选 WB 店铺，点「批量生成草稿」，确认框点确定</t>
+          <t>勾选1条点批量生成草稿并确定</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>草稿箱条数增加或出现来源「1688精选」；点该行「编辑」后产品类目仍为推荐预填</t>
+          <t>草稿箱全部计数+1；编辑后类目推荐预填</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>有货时执行；不要只断言页面有「草稿」二字</t>
+          <t>按条数差核对，不用1688精选四字</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>入口/空列表</t>
+          <t>入口/空或有货</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>展示「暂无淘宝精选商品」，共0条</t>
+          <t>无货暂无淘宝精选商品；有货出现一键刊登</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>有卡片商品（含一键刊登/offerId）时跳过空列表断言</t>
+          <t>两种环境都执行分支断言</t>
         </is>
       </c>
     </row>
@@ -3276,12 +3276,12 @@
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>补齐店铺、WB仓库、类目、标题、重量尺寸、主图、俄罗斯尺码、刊登价、合规库存后生成草稿并「批量校验」</t>
+          <t>补齐仓库尺码颜色后生成草稿并批量校验</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>草稿进入「可刊登」；提交刊登后进入刊登中心，状态由后台推进为刊登中/成功/失败</t>
+          <t>可刊登计数&gt;=1；默认不真实提交</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>测试失败可将货号设为 SIMULATE_FAIL</t>
+          <t>图片未转存等仍待完善则skip</t>
         </is>
       </c>
     </row>
@@ -3688,6 +3688,406 @@
       <c r="J63" t="inlineStr">
         <is>
           <t>test_tc62</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>WB商品刊登-带出核对</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1688链接已拉取样例</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>带出/标题价格图SKU</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>先读卡片再进入刊登页</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>标题/价格/图/SKU与卡片一致，货源链接含offer</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>test_tc63</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>WB商品刊登-带出核对</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1688精选有货</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>带出/标题价格图SKU</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>先读卡片再一键刊登WB</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>标题/价格/图/SKU与卡片一致</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>test_tc64</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>WB商品刊登-带出核对</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>京东精选有货</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>带出/标题价格货源链接</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>先读卡片再一键刊登WB</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>带出与卡片一致；货源地址含京东/sku</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>test_tc65</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>WB商品刊登-带出核对</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>淘宝精选有货</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>带出/标题价格货源链接</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>先读卡片再一键刊登WB</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>带出与卡片一致；货源地址含淘宝/offer</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>test_tc66</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>WB商品刊登-店铺</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>京东精选有货且存在OZON店铺</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>店铺/OZON不可刊登WB</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>目标店铺选OZON后一键刊登WB</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>不得把OZON店当作已选WB店</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>test_tc67</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>WB商品刊登-批量草稿</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>京东精选有货</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>弹窗/确定取消</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>勾选后先取消再确定批量草稿</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>取消条数不变；确定后出现京东精选来源</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>test_tc68</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>WB商品刊登-Ozon入口</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>1688链接已拉取卡片</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>入口/Ozon一键刊登</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>一键刊登选Ozon平台</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>进入Ozon流程或给出提示</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>test_tc69</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>登录</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>独立浏览器</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>登录/错误密码</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>错误账号密码点登录</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>停留登录页或提示错误</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>test_tc70</t>
         </is>
       </c>
     </row>
@@ -3703,7 +4103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3974,6 +4374,42 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>带出核对</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TC63-66 标题/货源价/SKU/图片与卡片一致；货源链接按入口核对</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>批量确认框</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TC68 取消不增加草稿，确定才写入来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>错误登录</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TC70 独立 Chrome，不复用已登录 session</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/erp_WB_test.xlsx
+++ b/erp_WB_test.xlsx
@@ -7,12 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="WB刊登测试用例" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="用例说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="WB刊登" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Ozon刊登" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WB刊登测试用例'!$A$1:$J$59</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -20,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,50 +27,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="微软雅黑"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -80,52 +46,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00D9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="00D9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D9D9D9"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -495,19 +423,13 @@
   <dimension ref="A1:J71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="48" customWidth="1" min="7" max="7"/>
-    <col width="52" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="42" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>序号</t>
@@ -559,2941 +481,2943 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="48" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>WB商品刊登-1688链接采集</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，进入「商品 &gt; 商品采集」，停留「手动采集 &gt; 1688商品链接采集」</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>入口/空值</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>链接输入框为空，点击「拉取商品」</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>不发起拉取，提示需输入1688商品详情链接</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr"/>
-    </row>
-    <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>WB商品刊登-1688链接采集</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，进入「商品 &gt; 商品采集」</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>入口/非法链接</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>输入非1688链接（如淘宝/京东/随意文本）后点击「拉取商品」</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>拉取失败并提示链接无效/不支持，不生成商品卡片</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr"/>
-    </row>
-    <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>WB商品刊登-1688链接采集</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，进入「商品 &gt; 商品采集」</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>入口/合法短链</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>输入短链 https://detail.1688.com/offer/726638874254.html 后点击「拉取商品」</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>成功展示商品卡片：标题、Offer ID 726638874254、价格、图片张数、SKU数量，并出现「查看详情」「一键刊登」「1688原链接」</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>实测标题含「26秋苎麻扎染可调节长款吊带裙」</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>WB商品刊登-1688链接采集</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，进入「商品 &gt; 商品采集」</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>入口/带追踪参数长链</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>粘贴含 src/pid/spm/clickid 等参数的1688详情长链后点击「拉取商品」</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>按 offerId 726638874254 成功拉取，结果与短链一致</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>https://detail.1688.com/offer/726638874254.html?src=zhanwai&amp;pid=301011_0000&amp;ptid=01770000000c8ba254ee13092cfbc8c0&amp;exp=enquiry%3AB%3BqueryMobilePhone%3AA%3Bxlyx%3AB</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>WB商品刊登-1688链接采集</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，进入「商品 &gt; 商品采集」</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>入口/多链接</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>同一输入框用逗号或换行填写多个1688详情链接后拉取</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>按链接分别拉取并展示多张商品卡片；非法链接单独失败不影响合法链接</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>页面提示支持逗号/换行分隔</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>WB商品刊登-1688链接采集</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，进入「商品 &gt; 商品采集」</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>入口/原链接</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>拉取成功后点击卡片「1688原链接」</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>新开/跳转至对应1688详情页，offerId一致</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>WB商品刊登-1688链接采集</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，进入「商品 &gt; 商品采集」，已拉取到商品卡片</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>入口/平台选择</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>点击「一键刊登」，检查下拉菜单</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>出现「WB 平台」「Ozon 平台」两项</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>WB商品刊登-1688链接采集</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，进入「商品 &gt; 商品采集」，已拉取到商品卡片</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>入口/进入刊登页</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>点击「一键刊登 &gt; WB 平台」</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>跳转 Wildberries 一键刊登页；来源标识为1688精选/offer 726638874254；标题、主图、SKU变体（7个）、采集价预填；产品类目已带出推荐类目（「荐」），不得为空</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>实测SKU=7、图片=5、价格约109；连衣裙预填「服装 / 连衣裙」</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>WB商品刊登-1688精选</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，进入「商品 &gt; 商品采集」</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>入口/页面加载</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>点击Tab「1688精选」</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>进入 #/goods/collection?tab=pallet，展示类目筛选、查询/重置、排序、目标店铺、本页全选、批量生成草稿</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr"/>
-    </row>
-    <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>WB商品刊登-1688精选</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>账号luojiaxing1已登录如斯达ERP，进入「商品 &gt; 商品采集」，1688精选无数据</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>账号luojiaxing1已登录如斯达ERP，进入「商品 &gt; 商品采集」</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>入口/空或有货</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>等待列表加载完成</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>无货展示暂无1688精选商品；有货则出现一键刊登卡片</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>无货展示「暂无1688精选商品」；有货则出现一键刊登卡片</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>两种环境都执行分支断言</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="48" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>WB商品刊登-1688精选</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，进入「商品 &gt; 商品采集」</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>入口/未勾选批量</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>不勾选商品，直接点「批量生成草稿」</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>提示先勾选1688精选商品，不生成草稿</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>京东精选同类提示为「请先勾选京东精选商品」</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>WB商品刊登-1688精选</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，进入「商品 &gt; 商品采集」，1688精选存在可售商品</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>入口/一键刊登WB</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>在商品卡点击「一键刊登 &gt; WB 平台」</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>进入WB一键刊登编辑页，货源信息、图片、规格、采集价从1688精选带入；目标店铺为已选WB店铺；产品类目自带推荐类目（「荐」）</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>有货时执行</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>WB商品刊登-1688精选</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，进入「商品 &gt; 商品采集」，1688精选存在可售商品</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>入口/批量草稿</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>勾选1条点批量生成草稿并确定</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>草稿箱全部计数+1；编辑后类目推荐预填</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>按条数差核对，不用1688精选四字</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="48" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>勾选1条，目标店铺选 WB 店铺，点「批量生成草稿」，确认框点确定</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>草稿箱「全部」计数 +1；编辑后类目仍为推荐预填（不用「1688精选」四字冒充链接稿）</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>有货时执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>WB商品刊登-1688精选</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，进入「商品 &gt; 商品采集」</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>入口/筛选排序</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>使用一/二/三级类目、关键词查询、同步时间/货源价排序</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>列表按条件刷新；重置后恢复默认</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr"/>
-    </row>
-    <row r="16" ht="48" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>WB商品刊登-京东精选</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，进入「商品 &gt; 商品采集」</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>入口/页面加载</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>点击Tab「京东精选」</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>进入 #/goods/collection?tab=jd-pallet，列表展示标题、skuId、类目、规格、货源价、「一键刊登」「查看货源」</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>实测有香薰类商品，skuId如100406854234</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="48" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>WB商品刊登-京东精选</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，进入「商品 &gt; 商品采集」</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>入口/查询</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>在「标题 / skuId」输入已知skuId后点查询</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>仅展示匹配商品；重置后恢复列表</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr"/>
-    </row>
-    <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>WB商品刊登-京东精选</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，进入「商品 &gt; 商品采集」</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>入口/查看货源</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>点击某条「查看货源」</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>跳转京东货源详情，skuId与卡片一致</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr"/>
-    </row>
-    <row r="19" ht="48" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>WB商品刊登-京东精选</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，进入「商品 &gt; 商品采集」</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>入口/未勾选批量</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>已选0条时点击「批量生成草稿」</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>提示「请先勾选京东精选商品」，不生成草稿</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>实测已出现该提示</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>WB商品刊登-京东精选</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，进入「商品 &gt; 商品采集」</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>入口/一键刊登WB</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>商品卡「一键刊登 &gt; WB 平台」</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>进入WB一键刊登编辑页；货源地址/规格/采集价来自京东精选；店铺为当前目标WB店铺；产品类目自带推荐类目（「荐」）</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>目标店铺需选[WB]店铺而非[OZON]</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="48" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>WB商品刊登-京东精选</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，进入「商品 &gt; 商品采集」</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>入口/目标店铺</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>目标店铺下拉检查选项</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>同时出现[WB]与[OZON]店铺；刊登WB时必须选择WB店铺</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>实测有天津智云、同江同智、Minjin等</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="48" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>WB商品刊登-京东精选</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，进入「商品 &gt; 商品采集」</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>入口/批量草稿</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>勾选1条，目标店铺选[WB]天津智云，点「批量生成草稿」，确认框点确定</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>草稿箱来源列出现「京东精选」（不能只看已有1688草稿）；点该行「编辑」后产品类目为推荐预填</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>有货时执行</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="48" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>WB商品刊登-淘宝精选</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，进入「商品 &gt; 商品采集」</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>入口/页面加载</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>点击Tab「淘宝精选」</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>进入 #/goods/collection?tab=taobao-pallet，筛选项与1688/京东精选结构一致（类目、查询、排序、目标店铺、批量生成草稿）</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J23" s="6" t="inlineStr"/>
-    </row>
-    <row r="24" ht="48" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>WB商品刊登-淘宝精选</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>账号luojiaxing1已登录如斯达ERP，进入「商品 &gt; 商品采集」，淘宝精选无数据</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>账号luojiaxing1已登录如斯达ERP，进入「商品 &gt; 商品采集」</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>入口/空或有货</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>等待加载完成</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>无货暂无淘宝精选商品；有货出现一键刊登</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>无货展示「暂无淘宝精选商品」；有货则出现一键刊登</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t>两种环境都执行分支断言</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="48" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>WB商品刊登-淘宝精选</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，进入「商品 &gt; 商品采集」</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>入口/未勾选批量</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>不勾选直接「批量生成草稿」</t>
         </is>
       </c>
-      <c r="H25" s="6" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>提示先勾选淘宝精选商品，不生成草稿</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J25" s="6" t="inlineStr"/>
-    </row>
-    <row r="26" ht="48" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>WB商品刊登-淘宝精选</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，进入「商品 &gt; 商品采集」，淘宝精选存在可售商品</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>入口/一键刊登WB</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>商品卡「一键刊登 &gt; WB 平台」</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>进入WB一键刊登编辑页，货源来自淘宝精选并预填标题/图片/规格/价格；产品类目自带推荐类目（「荐」）</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t>有货时执行</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="48" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>WB商品刊登-淘宝精选</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，进入「商品 &gt; 商品采集」，淘宝精选存在可售商品</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>入口/批量草稿</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>勾选1条并选择WB目标店铺后「批量生成草稿」，确认框点确定</t>
         </is>
       </c>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>草稿箱来源列出现「淘宝精选」（不能只看已有1688草稿）；点该行「编辑」后产品类目为推荐预填</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J27" s="6" t="inlineStr">
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
         <is>
           <t>有货时执行</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="48" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>WB商品刊登-刊登页必填</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，已从采集入口进入「Wildberries 一键刊登」编辑页</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>必填/上架店铺</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>上架店铺带红色*必填；清空或未选店铺后点「生成刊登草稿」或「一键刊登」</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>拦截提交，提示补选上架店铺；不进入刊登队列</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
         <is>
           <t>表单项 class=is-required</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="48" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>WB商品刊登-刊登页必填</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，已从采集入口进入「Wildberries 一键刊登」编辑页</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>必填/仓库</t>
         </is>
       </c>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>「选择仓库」为必填且为空（「选择 WB 仓库」占位）时保存/提交</t>
         </is>
       </c>
-      <c r="H29" s="6" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>草稿校验失败：涉及库存上传时请先拉取并选择WB仓库；草稿落入「待完善」</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J29" s="6" t="inlineStr">
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>实测校验文案含该提示</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="48" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>WB商品刊登-刊登页必填</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，已从采集入口进入「Wildberries 一键刊登」编辑页</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>必填/产品类目</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>进入页面时产品类目已带「荐」且已预填；清空类目后提交</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>进入时类目非空且有推荐标识；清空后拦截并提示选择Wildberries产品类目（subject）</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
         <is>
           <t>1688连衣裙实测预填「服装 / 连衣裙」</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="48" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>WB商品刊登-刊登页必填</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，已从采集入口进入「Wildberries 一键刊登」编辑页</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>必填/标题二选一</t>
         </is>
       </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>中文标题与俄语标题同时清空后提交</t>
         </is>
       </c>
-      <c r="H31" s="6" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>提示补填标题（中文与俄语标题二选一即可；都为空时提交会提示补填）</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J31" s="6" t="inlineStr">
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
         <is>
           <t>页面原文案</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="48" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>WB商品刊登-刊登页必填</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，已从采集入口进入「Wildberries 一键刊登」编辑页</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>格式/标题长度</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>中文或俄语标题输入超过60字</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>计数器显示上限60，无法继续输入或提交时提示超长</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
         <is>
           <t>控件为 31/60 样式</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="48" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>WB商品刊登-刊登页必填</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，已从采集入口进入「Wildberries 一键刊登」编辑页</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>必填/仅中文标题</t>
         </is>
       </c>
-      <c r="G33" s="6" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>只填中文标题、俄语标题为空，其余必填齐全后生成草稿</t>
         </is>
       </c>
-      <c r="H33" s="6" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>允许保存；俄语标题可为空（提交WB前建议再译）</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J33" s="6" t="inlineStr">
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
         <is>
           <t>页面写明二选一</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="48" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>WB商品刊登-刊登页必填</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，已从采集入口进入「Wildberries 一键刊登」编辑页</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>必填/仅俄语标题</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>只填俄语标题、中文标题为空，其余必填齐全后生成草稿</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>允许保存</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
         <is>
           <t>俄语标题为真实提交WB的标题</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="48" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>WB商品刊登-刊登页必填</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，已从采集入口进入「Wildberries 一键刊登」编辑页</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>非必填/品牌</t>
         </is>
       </c>
-      <c r="G35" s="6" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>品牌留空（占位「可选」）后保存草稿</t>
         </is>
       </c>
-      <c r="H35" s="6" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>不因品牌为空而校验失败</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J35" s="6" t="inlineStr"/>
-    </row>
-    <row r="36" ht="48" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>WB商品刊登-刊登页必填</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，已从采集入口进入「Wildberries 一键刊登」编辑页</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>必填/包装重量</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>包装重量 kg 带*；清空或填0/负数后提交</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>拦截并提示补填有效包装重量</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
         <is>
           <t>1688连衣裙实测预填0.8</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="48" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>WB商品刊登-刊登页必填</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，已从采集入口进入「Wildberries 一键刊登」编辑页</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>必填/包装尺寸</t>
         </is>
       </c>
-      <c r="G37" s="6" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>包装尺寸长/宽/高任一为空或非正数后提交</t>
         </is>
       </c>
-      <c r="H37" s="6" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>拦截并提示补齐包装尺寸 cm</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J37" s="6" t="inlineStr">
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
         <is>
           <t>实测预填长42宽32高5</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="48" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>WB商品刊登-刊登页必填</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，已从采集入口进入「Wildberries 一键刊登」编辑页</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>非必填/描述</t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>描述为空或填写卖点后保存</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>描述非红色必填，允许为空；填写时不超过2000字</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
         <is>
           <t>计数 31/2000</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="48" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>WB商品刊登-刊登页必填</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，已从采集入口进入「Wildberries 一键刊登」编辑页</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>非必填/商品编码前缀</t>
         </is>
       </c>
-      <c r="G39" s="6" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>前缀留空保存</t>
         </is>
       </c>
-      <c r="H39" s="6" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>不阻断草稿生成</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J39" s="6" t="inlineStr"/>
-    </row>
-    <row r="40" ht="48" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>WB商品刊登-刊登页必填</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，已从采集入口进入「Wildberries 一键刊登」编辑页</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>非必填/货源备注</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>货源备注占位「非必填」，留空保存</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>不阻断</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="inlineStr"/>
-    </row>
-    <row r="41" ht="48" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>WB商品刊登-刊登页必填</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，已从采集入口进入「Wildberries 一键刊登」编辑页</t>
         </is>
       </c>
-      <c r="F41" s="6" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>带出/货源地址</t>
         </is>
       </c>
-      <c r="G41" s="6" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>检查货源地址是否自动带出采集链接</t>
         </is>
       </c>
-      <c r="H41" s="6" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>1688入口带出 detail.1688.com/offer/726638874254.html；京东/淘宝入口带出对应货源链接</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J41" s="6" t="inlineStr"/>
-    </row>
-    <row r="42" ht="48" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>WB商品刊登-刊登页必填</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，已从采集入口进入「Wildberries 一键刊登」编辑页</t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>必填/主图图组</t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>删除全部商品主图后提交</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>提示需保留可用于变体引用的图片；采集图需转存素材区后才能提交WB</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
         <is>
           <t>页面说明图组不会直接提交WB</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="48" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>WB商品刊登-刊登页必填</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，已从采集入口进入「Wildberries 一键刊登」编辑页</t>
         </is>
       </c>
-      <c r="F43" s="6" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>素材/自动转存</t>
         </is>
       </c>
-      <c r="G43" s="6" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>从1688进入后观察主图/视频状态</t>
         </is>
       </c>
-      <c r="H43" s="6" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>展示「自动转存中」或转存成功；失败时不可一键刊登成功</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J43" s="6" t="inlineStr"/>
-    </row>
-    <row r="44" ht="48" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>WB商品刊登-刊登页必填</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，已从采集入口进入「Wildberries 一键刊登」编辑页</t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>必填/俄罗斯尺码</t>
         </is>
       </c>
-      <c r="G44" s="3" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>变体表「俄罗斯尺码*」为空时提交/校验</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>校验失败，要求为每个SKU填写俄罗斯尺码</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
         <is>
           <t>列头带*</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="48" customHeight="1">
-      <c r="A45" s="5" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>WB商品刊登-刊登页必填</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，已从采集入口进入「Wildberries 一键刊登」编辑页</t>
         </is>
       </c>
-      <c r="F45" s="6" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>必填/变体颜色</t>
         </is>
       </c>
-      <c r="G45" s="6" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>SKU行颜色未映射（「搜索并选择」为空）时校验</t>
         </is>
       </c>
-      <c r="H45" s="6" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>提示补齐变体颜色映射</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J45" s="6" t="inlineStr"/>
-    </row>
-    <row r="46" ht="48" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>WB商品刊登-刊登页必填</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，已从采集入口进入「Wildberries 一键刊登」编辑页</t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>必填/刊登价</t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>某SKU刊登价清空或&lt;=0后提交</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>拦截并提示补齐有效刊登价</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
         <is>
           <t>实测预填折后价104</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="48" customHeight="1">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>WB商品刊登-刊登页必填</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，已从采集入口进入「Wildberries 一键刊登」编辑页</t>
         </is>
       </c>
-      <c r="F47" s="6" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>格式/库存上限</t>
         </is>
       </c>
-      <c r="G47" s="6" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>任一SKU库存合计&gt;100000后校验</t>
         </is>
       </c>
-      <c r="H47" s="6" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>草稿校验失败，提示「库存不得超过100000」；状态为待完善</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J47" s="6" t="inlineStr">
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
         <is>
           <t>1688货源可售约1.9万，未超上限但草稿仍会因仓库缺失待完善</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="48" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>WB商品刊登-刊登页必填</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E48" s="3" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，已从采集入口进入「Wildberries 一键刊登」编辑页</t>
         </is>
       </c>
-      <c r="F48" s="3" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>必填/库存与分仓</t>
         </is>
       </c>
-      <c r="G48" s="3" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>库存&gt;0但分仓为「未分配」、未选WB仓库</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>校验提示请先拉取并选择WB仓库；不可进入「可刊登」</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J48" s="3" t="inlineStr"/>
-    </row>
-    <row r="49" ht="48" customHeight="1">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>WB商品刊登-刊登页必填</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，已从采集入口进入「Wildberries 一键刊登」编辑页</t>
         </is>
       </c>
-      <c r="F49" s="6" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>格式/WB Club折扣</t>
         </is>
       </c>
-      <c r="G49" s="6" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>填写Club折扣为1、2、32或负数后失焦</t>
         </is>
       </c>
-      <c r="H49" s="6" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>自动修正：仅允许0或3-31</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J49" s="6" t="inlineStr">
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
         <is>
           <t>列头说明「Club 折扣：0 或 3-31，失焦修正」</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="48" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>WB商品刊登-刊登页必填</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D50" s="8" t="inlineStr">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，已从采集入口进入「Wildberries 一键刊登」编辑页</t>
         </is>
       </c>
-      <c r="F50" s="3" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>非必填/卖家折扣</t>
         </is>
       </c>
-      <c r="G50" s="3" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>卖家折扣%留空</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>允许保存；不作为红色必填</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J50" s="3" t="inlineStr"/>
-    </row>
-    <row r="51" ht="48" customHeight="1">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>WB商品刊登-刊登页必填</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，已从采集入口进入「Wildberries 一键刊登」编辑页</t>
         </is>
       </c>
-      <c r="F51" s="6" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>带出/条形码</t>
         </is>
       </c>
-      <c r="G51" s="6" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>检查规格/货号条形码</t>
         </is>
       </c>
-      <c r="H51" s="6" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>系统自动生成且只读（占位「自动生成」）</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J51" s="6" t="inlineStr">
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
         <is>
           <t>实测如2014247971892</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="48" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>WB商品刊登-刊登页必填</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D52" s="8" t="inlineStr">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E52" s="3" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，已从采集入口进入「Wildberries 一键刊登」编辑页</t>
         </is>
       </c>
-      <c r="F52" s="3" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>非必填/类目扩展属性</t>
         </is>
       </c>
-      <c r="G52" s="3" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>连衣裙类目共享属性（纽扣类型、领口、风格等）全部留空后保存草稿</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>扩展属性默认非全部必填，不单独阻断草稿；按类目若出现红色*则该项必填</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
         <is>
           <t>可展开剩余39项</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="48" customHeight="1">
-      <c r="A53" s="5" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="B53" s="6" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>WB商品刊登-草稿提交</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，已从采集入口进入「Wildberries 一键刊登」编辑页，必填项未齐（缺仓库、缺俄罗斯尺码）</t>
         </is>
       </c>
-      <c r="F53" s="6" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>流程/生成草稿</t>
         </is>
       </c>
-      <c r="G53" s="6" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>点击「生成刊登草稿」</t>
         </is>
       </c>
-      <c r="H53" s="6" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>生成前刊登页已带推荐类目；提示已生成刊登草稿；跳转草稿箱；来源含一键WB刊登；校验列展示待完善原因；计数「待完善」+1、「可刊登」不加</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J53" s="6" t="inlineStr">
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
         <is>
           <t>实测来源：1688精选/offer 726638874254 · 一键WB刊登</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="48" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>WB商品刊登-草稿提交</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，进入「商品 &gt; WB商品刊登」草稿箱，存在待完善草稿</t>
         </is>
       </c>
-      <c r="F54" s="3" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>流程/待完善不可刊登</t>
         </is>
       </c>
-      <c r="G54" s="3" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>不勾选或勾选待完善草稿后看「提交刊登」；或点行内「提交刊登」</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>批量提交刊登在非「可刊登」时不可用；未通过校验的草稿不能进入刊登队列，提示先批量校验或完善必填</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
         <is>
           <t>页面：仅「可刊登」可批量提交</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="48" customHeight="1">
-      <c r="A55" s="5" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>WB商品刊登-草稿提交</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，已从采集入口进入「Wildberries 一键刊登」编辑页</t>
         </is>
       </c>
-      <c r="F55" s="6" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>流程/必填齐全可刊登</t>
         </is>
       </c>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>补齐仓库尺码颜色后生成草稿并批量校验</t>
-        </is>
-      </c>
-      <c r="H55" s="6" t="inlineStr">
-        <is>
-          <t>可刊登计数&gt;=1；默认不真实提交</t>
-        </is>
-      </c>
-      <c r="I55" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J55" s="6" t="inlineStr">
-        <is>
-          <t>图片未转存等仍待完善则skip</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="48" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>补齐仓库、俄罗斯尺码、颜色映射后生成草稿并「批量校验」</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>「可刊登」计数&gt;=1；默认不真实提交 WB（ERP_SUBMIT_LIVE=0）</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>图片未转存等导致仍待完善时 skip</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>WB商品刊登-草稿提交</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，进入「商品 &gt; WB商品刊登」草稿箱</t>
         </is>
       </c>
-      <c r="F56" s="3" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>流程/编辑回填</t>
         </is>
       </c>
-      <c r="G56" s="3" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>草稿箱点击「编辑」</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>回到一键刊登页且原填写/带出数据保留；产品类目仍为推荐预填（「荐」）</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J56" s="3" t="inlineStr"/>
-    </row>
-    <row r="57" ht="48" customHeight="1">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="B57" s="6" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>WB商品刊登-草稿提交</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D57" s="8" t="inlineStr">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，已从采集入口进入「Wildberries 一键刊登」编辑页</t>
         </is>
       </c>
-      <c r="F57" s="6" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>流程/取消</t>
         </is>
       </c>
-      <c r="G57" s="6" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>点击底部「取消」</t>
         </is>
       </c>
-      <c r="H57" s="6" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>离开编辑页且不新增草稿（或按页面确认框选择）</t>
         </is>
       </c>
-      <c r="I57" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J57" s="6" t="inlineStr"/>
-    </row>
-    <row r="58" ht="48" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>WB商品刊登-草稿提交</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D58" s="7" t="inlineStr">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，已从采集入口进入「Wildberries 一键刊登」编辑页</t>
         </is>
       </c>
-      <c r="F58" s="3" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>一致性/多入口同页</t>
         </is>
       </c>
-      <c r="G58" s="3" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>分别从1688链接、1688精选、京东精选、淘宝精选进入WB一键刊登</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>均为同一套三步表单（基本信息/产品属性/变体设置），必填规则一致，仅货源来源字段不同；各入口产品类目均自带推荐类目</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J58" s="3" t="inlineStr"/>
-    </row>
-    <row r="59" ht="48" customHeight="1">
-      <c r="A59" s="5" t="inlineStr">
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="B59" s="6" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>WB商品刊登-推荐类目</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E59" s="6" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>账号luojiaxing1已登录如斯达ERP，可从1688链接/1688精选/京东精选/淘宝精选进入刊登或草稿编辑</t>
         </is>
       </c>
-      <c r="F59" s="6" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>带出/推荐类目</t>
         </is>
       </c>
-      <c r="G59" s="6" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>各入口点「一键刊登 &gt; WB」进入刊登页；生成草稿后点「编辑」进入草稿页</t>
         </is>
       </c>
-      <c r="H59" s="6" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>产品类目均已预填且带「荐」，不得为空、不得要求从零手选；精选无货时该入口跳过</t>
         </is>
       </c>
-      <c r="I59" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="J59" s="6" t="inlineStr">
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
         <is>
           <t>对应脚本 test_tc58</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="n">
-        <v>59</v>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -3542,8 +3466,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="n">
-        <v>60</v>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -3592,8 +3518,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="n">
-        <v>61</v>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -3642,8 +3570,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="n">
-        <v>62</v>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -3677,7 +3607,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>重量/长宽高与原商品一致；原商品没有的项刊登页留空；无货跳过</t>
+          <t>重量/长宽高与原商品一致；卡片未展示包装则跳过；无货跳过</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3692,8 +3622,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="n">
-        <v>63</v>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -3722,12 +3654,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>先读卡片再进入刊登页</t>
+          <t>先读卡片标题/货源价/SKU/图片数，再进入刊登页</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>标题/价格/图/SKU与卡片一致，货源链接含offer</t>
+          <t>标题包含卡片文案；采集价或刊登价与货源价一致；有主图；SKU 行数可对上；货源链接含 offer</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3742,8 +3674,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="n">
-        <v>64</v>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -3772,12 +3706,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>先读卡片再一键刊登WB</t>
+          <t>先读卡片再一键刊登 WB</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>标题/价格/图/SKU与卡片一致</t>
+          <t>标题/价格/图/SKU 与卡片一致</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3792,8 +3726,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="n">
-        <v>65</v>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -3822,12 +3758,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>先读卡片再一键刊登WB</t>
+          <t>先读卡片再一键刊登 WB</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>带出与卡片一致；货源地址含京东/sku</t>
+          <t>带出字段与卡片一致；货源地址含京东/sku</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3842,8 +3778,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="n">
-        <v>66</v>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -3872,12 +3810,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>先读卡片再一键刊登WB</t>
+          <t>先读卡片再一键刊登 WB</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>带出与卡片一致；货源地址含淘宝/offer</t>
+          <t>带出字段与卡片一致；货源地址含淘宝/offer</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3892,8 +3830,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="n">
-        <v>67</v>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -3912,7 +3852,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>京东精选有货且存在OZON店铺</t>
+          <t>京东精选有货且存在 OZON 店铺</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3922,12 +3862,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>目标店铺选OZON后一键刊登WB</t>
+          <t>目标店铺选 OZON 后一键刊登 WB</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>不得把OZON店当作已选WB店</t>
+          <t>上架店铺不得把 OZON 店当作已选 WB 店，或仍要求补选 WB 店铺</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3942,8 +3882,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
-        <v>68</v>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -3972,12 +3914,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>勾选后先取消再确定批量草稿</t>
+          <t>勾选后批量生成：先点取消再点确定</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>取消条数不变；确定后出现京东精选来源</t>
+          <t>取消后草稿箱条数不变；确定后出现来源京东精选</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3992,8 +3934,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="n">
-        <v>69</v>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -4022,12 +3966,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>一键刊登选Ozon平台</t>
+          <t>见 Ozon 用例 OZ01 / OZ20</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>进入Ozon流程或给出提示</t>
+          <t>已迁至 Ozon 套件</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4037,13 +3981,15 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>test_tc69</t>
+          <t>原 test_tc69</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="n">
-        <v>70</v>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -4062,7 +4008,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>独立浏览器</t>
+          <t>未登录或独立浏览器</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4072,12 +4018,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>错误账号密码点登录</t>
+          <t>输入错误账号密码点登录</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>停留登录页或提示错误</t>
+          <t>停留登录页或提示密码/账号错误</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4087,12 +4033,11 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>test_tc70</t>
+          <t>test_tc70 独立 Chrome</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4103,310 +4048,1260 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>字段</t>
-        </is>
-      </c>
-      <c r="B1" s="9" t="inlineStr">
-        <is>
-          <t>说明</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>功能名称</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>用例类型</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>用例等级</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>前置条件</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>维度</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>校验点</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>期待值</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>用例状态</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>环境</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>https://russtar.wildberries.center</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>OZ01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ozon商品刊登-入口</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1688链接已拉取卡片</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>入口/1688链接</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>一键刊登 &gt; Ozon 平台</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>进入 Ozon 刊登编辑页；offer 预填；类目自带「荐」</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>test_oz01</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>账号</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>luojiaxing1</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>OZ02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ozon商品刊登-入口</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1688精选有货</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>入口/1688精选</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>目标店选 OZON 后一键 Ozon</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>进入 Ozon 刊登页；类目自带「荐」</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>test_oz02</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>推荐类目</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>任一入口进入 WB 一键刊登页或草稿编辑页，产品类目必须已预填且带「荐」</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>OZ03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ozon商品刊登-入口</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>京东精选有货</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>入口/京东精选</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>目标店选 OZON 后一键 Ozon</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>进入 Ozon 刊登页；类目自带「荐」</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>test_oz03</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>入口</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>1688链接采集、1688精选、京东精选、淘宝精选</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>OZ04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ozon商品刊登-入口</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>淘宝精选有货</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>入口/淘宝精选</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>目标店选 OZON 后一键 Ozon</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>进入 Ozon 刊登页；类目自带「荐」</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>test_oz04</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>失败重试</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>pytest-rerunfailures；pytestmark = pytest.mark.flaky(reruns=2, reruns_delay=3)</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>OZ05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ozon商品刊登-入口</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>京东精选可打开</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>入口/目标店铺</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>目标店铺下拉</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>出现 OZON 店铺</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>test_oz05</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>日志</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>utils/logger.py；reports/logs/erp_wb.log；关弹窗打 WARNING</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>OZ06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ozon商品刊登-刊登页必填</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>已从1688进入 Ozon 刊登页</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>必填/上架店铺</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>检查上架店铺</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>店铺为必填</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>test_oz06</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>兜底关弹窗</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>BasePage.dismiss_popups() 在点击/填表/跳转前调用；无弹窗不报错；toast() 前不调用</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>OZ07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ozon商品刊登-刊登页必填</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>已从1688进入 Ozon 刊登页</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>必填/产品类目</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>检查类目</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>已预填且带「荐」，不得为空</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>test_oz07</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>刊登页判定</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>仅 URL 含 wb-one-click-listing 视为刊登编辑页；拉取成功须出现 offerId+一键刊登，不能把 toast 当成功</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>OZ08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ozon商品刊登-刊登页必填</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>已从1688进入 Ozon 刊登页</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>必填/标题</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>检查标题</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>标题控件存在且可读取</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>test_oz08</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Allure</t>
+          <t>OZ09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>pytest 写入 reports/allure-results；浏览器查看：allure serve reports/allure-results（不要直接看 JSON）</t>
+          <t>Ozon商品刊登-刊登页必填</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>已从1688进入 Ozon 刊登页</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>带出/货源地址</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>检查货源链接</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>含 1688 offer</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>test_oz09</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>模块路径</t>
+          <t>OZ10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>商品 &gt; 商品采集 / 商品 &gt; WB商品刊登</t>
+          <t>Ozon商品刊登-刊登页必填</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>已从1688进入 Ozon 刊登页</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>必填/主图</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>删除全部主图后保存</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>拦截并提示图片/主图</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>test_oz10</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1688链接</t>
+          <t>OZ11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://detail.1688.com/offer/726638874254.html</t>
+          <t>Ozon商品刊登-刊登页必填</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>已从1688进入 Ozon 刊登页</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>素材/主图带出</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>检查主图数量</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>至少 1 张</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>test_oz11</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>入口对照</t>
+          <t>OZ12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>手动采集-1688商品链接采集；1688精选 tab=pallet；京东精选 tab=jd-pallet；淘宝精选 tab=taobao-pallet</t>
+          <t>Ozon商品刊登-刊登页必填</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>已从1688进入 Ozon 刊登页</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>必填/价格</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>检查价格控件</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>存在刊登价/采集价/售价</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>test_oz12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>刊登页必填（红色*）</t>
+          <t>OZ13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>上架店铺、选择仓库、产品类目、包装重量kg、包装尺寸cm、变体俄罗斯尺码*</t>
+          <t>Ozon商品刊登-草稿</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>已从1688进入 Ozon 刊登页</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>流程/生成草稿</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>生成刊登草稿</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>出现草稿提示或进入草稿箱</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>test_oz13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>标题规则</t>
+          <t>OZ14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>中文标题与俄语标题二选一；上限各60字；都为空提交失败</t>
+          <t>Ozon商品刊登-草稿</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>已从1688进入 Ozon 刊登页</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>流程/取消</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>点取消</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>离开 Ozon 编辑页</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>test_oz14</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>库存规则</t>
+          <t>OZ15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>库存不得超过100000；涉及库存上传须先拉取并选择WB仓库</t>
+          <t>Ozon商品刊登-包装带出</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1688样例已拉取</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>带出/包装</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>核对重量尺寸</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>与原商品一致；无包装则 skip</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>test_oz15</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Club折扣</t>
+          <t>OZ16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0 或 3-31，失焦自动修正</t>
+          <t>Ozon商品刊登-带出核对</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1688样例已拉取</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>带出/标题价格图</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>先读卡片再进 Ozon 页</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>标题/主图带出</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>test_oz16</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>草稿校验</t>
+          <t>OZ17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>含标题、类目、库存与 attrJson 合法 JSON；仅「可刊登」可批量提交</t>
+          <t>Ozon商品刊登-包装带出</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1688精选有货</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>带出/包装</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>核对重量尺寸</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>与原商品一致；无包装则 skip</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>test_oz17</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>当前环境备注</t>
+          <t>OZ18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1688精选、淘宝精选列表为空；京东精选有数据；1688链接726638874254可拉取成功</t>
+          <t>Ozon商品刊登-一致性</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>各精选可打开</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>一致性/多入口</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>四入口进 Ozon 页</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>表单结构一致；各类目均自带「荐」</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>test_oz18</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>批量草稿来源</t>
+          <t>OZ19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TC13/21/26 须在草稿箱核对来源列（1688精选/京东精选/淘宝精选）；确认框点确定，勿点取消</t>
+          <t>Ozon商品刊登-店铺</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>京东精选有货</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>店铺/WB不可当Ozon店</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>目标店选 WB 后一键 Ozon</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>不得把 WB 店当成已选 Ozon 店，或提示选 OZON 店</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>test_oz19</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>精选卡片有货</t>
+          <t>OZ20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1688/淘宝精选为卡片：有货认一键刊登下拉或 offerId：数字；勾选卡片复选框，不要只找表格 button</t>
+          <t>Ozon商品刊登-入口</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1688卡片已拉取</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>入口/菜单</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>一键刊登下拉</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>含 Ozon 平台</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>test_oz20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>包装带出</t>
+          <t>OZ21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>包装带出须与原商品一致：卡片/查看详情有值则刊登页相等；没有则留空。TC59 样例 0.8kg 42x32x5。</t>
+          <t>Ozon商品刊登-包装带出</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>京东精选有货</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>带出/包装</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>先读原商品再一键 Ozon</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>重量/长宽高与原商品一致；卡片未展示包装则 skip</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>test_oz21</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>带出核对</t>
+          <t>OZ22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TC63-66 标题/货源价/SKU/图片与卡片一致；货源链接按入口核对</t>
+          <t>Ozon商品刊登-包装带出</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>淘宝精选有货</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>带出/包装</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>先读原商品再一键 Ozon</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>重量/长宽高与原商品一致；卡片未展示包装则 skip</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>test_oz22</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>批量确认框</t>
+          <t>OZ23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TC68 取消不增加草稿，确定才写入来源</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>错误登录</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>TC70 独立 Chrome，不复用已登录 session</t>
+          <t>Ozon商品刊登-推荐类目</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>可从四入口进入 Ozon 刊登或草稿编辑</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>带出/推荐类目</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>各入口点 Ozon 进入刊登页；生成草稿后点编辑</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>产品类目均已预填且带「荐」；精选无货时该入口跳过</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>test_oz23</t>
         </is>
       </c>
     </row>

--- a/erp_WB_test.xlsx
+++ b/erp_WB_test.xlsx
@@ -4048,7 +4048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>检查标题</t>
+          <t>清空标题后保存</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>标题控件存在且可读取</t>
+          <t>拦截并提示补填标题</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4714,12 +4714,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>检查价格控件</t>
+          <t>清空刊登价/售价后保存</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>存在刊登价/采集价/售价</t>
+          <t>拦截并提示补齐有效价格</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>出现草稿提示或进入草稿箱</t>
+          <t>进入 Ozon 草稿箱；可见待完善/可刊登/校验，且来源含 Ozon 或 1688/offer</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>标题/主图带出</t>
+          <t>标题/价格/主图带出；货源含 offer</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>表单结构一致；各类目均自带「荐」</t>
+          <t>表单结构一致（荐由 OZ01-04 / OZ23 覆盖）</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -5302,6 +5302,942 @@
       <c r="J24" t="inlineStr">
         <is>
           <t>test_oz23</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>OZ24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ozon商品刊登-刊登页必填</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>已从1688进入 Ozon 刊登页</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>必填/包装重量</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>清空或填 0 后保存</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>拦截并提示补填有效包装重量</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>test_oz24</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>OZ25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Ozon商品刊登-刊登页必填</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>已从1688进入 Ozon 刊登页</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>必填/包装尺寸</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>清空长宽高后保存</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>拦截并提示补齐包装尺寸</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>test_oz25</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>OZ26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Ozon商品刊登-带出核对</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1688精选有货</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>带出/标题价格图</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>先读卡片再一键 Ozon</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>标题/价格/图与卡片一致</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>test_oz26</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>OZ27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Ozon商品刊登-带出核对</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>京东精选有货</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>带出/标题价格货源链接</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>先读卡片再一键 Ozon</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>带出字段与卡片一致；货源含京东/sku</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>test_oz27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>OZ28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ozon商品刊登-带出核对</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>淘宝精选有货</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>带出/标题价格货源链接</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>先读卡片再一键 Ozon</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>带出字段与卡片一致；货源含淘宝/offer</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>test_oz28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>OZ29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Ozon商品刊登-批量草稿</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>京东精选有货</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>入口/批量草稿</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>目标店选 OZON，勾选后批量生成草稿</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Ozon 草稿箱来源列含「京东精选」或 Ozon 标识</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>test_oz29</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>OZ30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Ozon商品刊登-草稿</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>已生成 Ozon 草稿</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>流程/待完善不可刊登</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>看提交刊登</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>待完善时不可批量提交，或需先校验</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>test_oz30</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>OZ31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Ozon商品刊登-草稿</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>已生成 Ozon 草稿</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>流程/编辑回填</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>草稿箱点编辑</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>回到 Ozon 刊登页，标题或推荐类目保留</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>test_oz31</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>OZ32</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Ozon商品刊登-精选入口</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>可打开三精选且可选 OZON 店</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>入口/页面结构</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>目标店选 OZON 后看筛选与列表</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>有查询/重置/排序/批量生成草稿；有货见一键刊登，无货见暂无</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>test_oz32</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>OZ33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Ozon商品刊登-精选入口</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>三精选可打开且可选 OZON 店</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>入口/未勾选批量</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>不勾选直接批量生成草稿</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>提示先勾选，不生成草稿</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>test_oz33</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>OZ34</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Ozon商品刊登-批量草稿</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1688精选有货</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>入口/批量草稿</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>目标店选 OZON，勾选后批量生成</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Ozon 草稿箱来源含「1688精选」</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>test_oz34</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>OZ35</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Ozon商品刊登-批量草稿</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>淘宝精选有货</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>入口/批量草稿</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>目标店选 OZON，勾选后批量生成</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Ozon 草稿箱来源含「淘宝精选」</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>test_oz35</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>OZ36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Ozon商品刊登-批量草稿</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>京东精选有货</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>弹窗/确定取消</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>目标店选 OZON：先取消再确定</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>取消后条数不变；确定后来源含「京东精选」</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>test_oz36</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>OZ37</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Ozon商品刊登-刊登页必填</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>已从1688进入 Ozon 刊登页</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>必填/产品类目</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>清空已预填类目后保存</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>拦截并提示补选类目</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>test_oz37</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>OZ38</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Ozon商品刊登-刊登页必填</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>已从1688进入 Ozon 刊登页</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>格式/标题长度</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>输入超长标题</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>按页面 maxlength 或计数上限截断，不写死 WB 的 60 字</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>test_oz38</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>OZ39</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Ozon商品刊登-刊登页必填</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>已从1688进入 Ozon 刊登页</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>非必填/品牌描述备注</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>检查页面上已有的品牌、描述、编码前缀、货源备注</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>出现的项不是红色必填；无这些控件则只确认产品属性区</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>test_oz39</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>OZ40</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Ozon商品刊登-刊登页必填</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>已从1688进入 Ozon 刊登页</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>素材/自动转存</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>看主图与转存/素材文案</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>至少 1 张主图，页面含转存、素材或主图说明</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>test_oz40</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>OZ41</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Ozon商品刊登-草稿</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>已从1688进入 Ozon 刊登页</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>流程/可刊登</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>有仓库则选择，生成草稿后批量校验</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>「可刊登」&gt;=1；默认不真实提交；无校验或仍待完善则 skip</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>test_oz41</t>
         </is>
       </c>
     </row>

--- a/erp_WB_test.xlsx
+++ b/erp_WB_test.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -919,7 +919,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>进入 #/goods/collection?tab=pallet，展示类目筛选、查询/重置、排序、目标店铺、本页全选、批量生成草稿</t>
+          <t>进入 #/goods/collection?tab=pallet，展示类目筛选、查询/重置、排序、目标店铺、本页全选、批量采集到草稿箱</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>不勾选商品，直接点「批量生成草稿」</t>
+          <t>不勾选商品，直接点「批量采集到草稿箱」</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>提示先勾选1688精选商品，不生成草稿</t>
+          <t>提示先勾选1688精选商品，不打开写入或未生成草稿</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>入口/批量草稿</t>
+          <t>入口/多店铺批量草稿</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>勾选1条，目标店铺选 WB 店铺，点「批量生成草稿」，确认框点确定</t>
+          <t>勾选1条，点「批量采集到草稿箱」，先勾 Wildberries，再勾至少 2 个具体 WB 店铺后点「完成」</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>草稿箱「全部」计数 +1；编辑后类目仍为推荐预填（不用「1688精选」四字冒充链接稿）</t>
+          <t>只勾平台不算选完；将写入 N 个具体店铺且 N≥2；草稿箱条数至少 +N；编辑后类目仍为推荐预填</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>有货时执行</t>
+          <t>店铺不足 2 家则 skip</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>已选0条时点击「批量生成草稿」</t>
+          <t>已选0条时点击「批量采集到草稿箱」</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1517,17 +1517,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>入口/批量草稿</t>
+          <t>入口/多店铺批量草稿</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>勾选1条，目标店铺选[WB]天津智云，点「批量生成草稿」，确认框点确定</t>
+          <t>勾选1条，先勾 Wildberries，再勾至少 2 个具体 WB 店铺后点「完成」</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>草稿箱来源列出现「京东精选」（不能只看已有1688草稿）；点该行「编辑」后产品类目为推荐预填</t>
+          <t>只勾平台不算选完；将写入 N≥2；草稿箱来源列出现「京东精选」，条数至少 +N；编辑后类目为推荐预填</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>进入 #/goods/collection?tab=taobao-pallet，筛选项与1688/京东精选结构一致（类目、查询、排序、目标店铺、批量生成草稿）</t>
+          <t>进入 #/goods/collection?tab=taobao-pallet，筛选项与1688/京东精选结构一致（类目、查询、排序、目标店铺、批量采集到草稿箱）</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>不勾选直接「批量生成草稿」</t>
+          <t>不勾选直接「批量采集到草稿箱」</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1769,17 +1769,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>入口/批量草稿</t>
+          <t>入口/多店铺批量草稿</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>勾选1条并选择WB目标店铺后「批量生成草稿」，确认框点确定</t>
+          <t>勾选1条，先勾 Wildberries，再勾至少 2 个具体 WB 店铺后点「完成」</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>草稿箱来源列出现「淘宝精选」（不能只看已有1688草稿）；点该行「编辑」后产品类目为推荐预填</t>
+          <t>只勾平台不算选完；将写入 N≥2；草稿箱来源列出现「淘宝精选」，条数至少 +N；编辑后类目为推荐预填</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3245,17 +3245,17 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>流程/编辑回填</t>
+          <t>流程/编辑后再打开核对</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>草稿箱点击「编辑」</t>
+          <t>草稿箱点击「编辑」，确认带回推荐类目后修改标题、描述、货源备注、包装和价格并保存，再从草稿箱打开同一条</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>回到一键刊登页且原填写/带出数据保留；产品类目仍为推荐预填（「荐」）</t>
+          <t>再次进入后每个改过的字段仍是修改后的值，不能只看页面上还有「荐」</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3263,7 +3263,11 @@
           <t>待执行</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>test_tc55</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3909,17 +3913,17 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>弹窗/确定取消</t>
+          <t>弹窗/多店铺确定取消</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>勾选后批量生成：先点取消再点确定</t>
+          <t>勾选后打开店铺弹窗：先关闭，再勾至少 2 个具体 WB 店铺点「完成」</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>取消后草稿箱条数不变；确定后出现来源京东精选</t>
+          <t>只勾平台不算选完；关闭后条数不变；完成后将写入 N≥2，来源为京东精选且条数至少 +N</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4034,6 +4038,110 @@
       <c r="J71" t="inlineStr">
         <is>
           <t>test_tc70 独立 Chrome</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>WB商品刊登-手动采集</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>1688链接已拉取商品卡</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>入口/多店铺采集到草稿箱</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>勾选商品，点「采集到草稿箱」，先勾 Wildberries，再勾至少 2 个具体店铺后点「完成」</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>只勾平台不算选完；将写入 N≥2；WB 草稿箱条数至少 +N，且能看到 1688 或 offer</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>test_tc71</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>WB商品刊登-草稿编辑</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>WB 草稿箱（#/goods/publish?tab=draft）有可编辑草稿；没有则先从1688生成一条</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>流程/修改后再打开</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>点行内「编辑」进入刊登页，修改中文/俄语标题、描述、货源备注、可输入的品牌、包装重量 1.25、尺寸 41×31×6、刊登价 188 后点「生成刊登草稿」，再从草稿箱打开同一条</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>再次进入后已改字段仍是修改后的值；类目仍带「荐」。下拉品牌不硬写。不点「提交刊登」</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>test_tc72</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5593,17 +5701,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>入口/批量草稿</t>
+          <t>入口/多店铺批量草稿</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>目标店选 OZON，勾选后批量生成草稿</t>
+          <t>勾选后先勾 Ozon，再勾至少 2 个具体 Ozon 店铺，点「完成」</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Ozon 草稿箱来源列含「京东精选」或 Ozon 标识</t>
+          <t>只勾平台不算选完；将写入 N≥2；Ozon 草稿箱来源含「京东精选」</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -5687,27 +5795,27 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>已生成 Ozon 草稿</t>
+          <t>已从1688进入 Ozon 刊登页</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>流程/编辑回填</t>
+          <t>流程/编辑后再打开核对</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>草稿箱点编辑</t>
+          <t>修改标题、描述、货源备注、包装和价格后保存，再从 Ozon 草稿箱点「编辑」打开同一条</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>回到 Ozon 刊登页，标题或推荐类目保留</t>
+          <t>再次进入后每个改过的字段仍是修改后的值；类目仍带「荐」。不能只因页面有「荐」就算通过</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -5853,17 +5961,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>入口/批量草稿</t>
+          <t>入口/多店铺批量草稿</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>目标店选 OZON，勾选后批量生成</t>
+          <t>先勾 Ozon，再勾至少 2 个具体店铺后点「完成」</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Ozon 草稿箱来源含「1688精选」</t>
+          <t>只勾平台不算选完；将写入 N≥2；Ozon 草稿箱来源含「1688精选」</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -5905,17 +6013,17 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>入口/批量草稿</t>
+          <t>入口/多店铺批量草稿</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>目标店选 OZON，勾选后批量生成</t>
+          <t>先勾 Ozon，再勾至少 2 个具体店铺后点「完成」</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Ozon 草稿箱来源含「淘宝精选」</t>
+          <t>只勾平台不算选完；将写入 N≥2；Ozon 草稿箱来源含「淘宝精选」</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -5957,17 +6065,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>弹窗/确定取消</t>
+          <t>弹窗/多店铺确定取消</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>目标店选 OZON：先取消再确定</t>
+          <t>先关闭店铺弹窗，再勾至少 2 个具体 Ozon 店铺后点「完成」</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>取消后条数不变；确定后来源含「京东精选」</t>
+          <t>只勾平台不算选完；关闭后条数不变；完成后将写入 N≥2，来源含「京东精选」且条数至少 +N</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -6238,6 +6346,110 @@
       <c r="J42" t="inlineStr">
         <is>
           <t>test_oz41</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>OZ42</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Ozon商品刊登-手动采集</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1688链接已拉取商品卡</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>入口/多店铺采集到草稿箱</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>勾选商品，采集到草稿箱时先勾 Ozon，再勾至少 2 个具体店铺后点「完成」</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>只勾平台不算选完；将写入 N≥2；Ozon 草稿箱条数至少 +N，且能看到 offer 或 Ozon</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>test_oz42</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>OZ43</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Ozon商品刊登-草稿编辑</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Ozon 草稿箱（#/goods/publish?tab=ozon/draft）有可编辑草稿；没有则先从1688生成一条</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>流程/修改后再打开</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>点行内「编辑」进入 Ozon 刊登页，修改标题、描述、货源备注、可输入的品牌、包装重量 1.25、尺寸 41×31×6、售价 188 后保存，再从草稿箱打开同一条</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>再次进入后已改字段仍是修改后的值；类目仍带「荐」。不改仓库、俄码、Club，不点「提交刊登」</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>test_oz43</t>
         </is>
       </c>
     </row>

--- a/erp_WB_test.xlsx
+++ b/erp_WB_test.xlsx
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>提示先勾选1688精选商品，不打开写入或未生成草稿</t>
+          <t>提示「请先勾选」，不勾店铺、不点完成，不生成草稿</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>勾选1条，点「批量采集到草稿箱」，先勾 Wildberries，再勾至少 2 个具体 WB 店铺后点「完成」</t>
+          <t>勾选1条，点「批量采集到草稿箱」，先勾 Wildberries，再勾同江和 Minjin后点「完成」</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>只勾平台不算选完；将写入 N 个具体店铺且 N≥2；草稿箱条数至少 +N；编辑后类目仍为推荐预填</t>
+          <t>只勾平台不算选完；将写入 N 个具体店铺且 N≥2；两边来源都含「1688精选」，WB 草稿箱至少 +1（同江），Ozon 草稿箱至少 +1（Minjin）；编辑后类目仍为推荐预填</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>提示「请先勾选京东精选商品」，不生成草稿</t>
+          <t>提示「请先勾选京东精选商品」，不勾店铺、不点完成，不生成草稿</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1522,12 +1522,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>勾选1条，先勾 Wildberries，再勾至少 2 个具体 WB 店铺后点「完成」</t>
+          <t>勾选1条，先勾 Wildberries，再勾同江和 Minjin后点「完成」</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>只勾平台不算选完；将写入 N≥2；草稿箱来源列出现「京东精选」，条数至少 +N；编辑后类目为推荐预填</t>
+          <t>只勾平台不算选完；将写入 N≥2；两边来源都含「京东精选」，WB 草稿箱至少 +1（同江），Ozon 草稿箱至少 +1（Minjin）；编辑后类目为推荐预填</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>提示先勾选淘宝精选商品，不生成草稿</t>
+          <t>提示「请先勾选」，不勾店铺、不点完成，不生成草稿</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>勾选1条，先勾 Wildberries，再勾至少 2 个具体 WB 店铺后点「完成」</t>
+          <t>勾选1条，先勾 Wildberries，再勾同江和 Minjin后点「完成」</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>只勾平台不算选完；将写入 N≥2；草稿箱来源列出现「淘宝精选」，条数至少 +N；编辑后类目为推荐预填</t>
+          <t>只勾平台不算选完；将写入 N≥2；两边来源都含「淘宝精选」，WB 草稿箱至少 +1（同江），Ozon 草稿箱至少 +1（Minjin）；编辑后类目为推荐预填</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3918,12 +3918,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>勾选后打开店铺弹窗：先关闭，再勾至少 2 个具体 WB 店铺点「完成」</t>
+          <t>勾选后打开店铺弹窗：先关闭，再勾同江和 Minjin点「完成」</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>只勾平台不算选完；关闭后条数不变；完成后将写入 N≥2，来源为京东精选且条数至少 +N</t>
+          <t>只勾平台不算选完；关闭后 WB 和 Ozon 草稿箱条数都不变；完成后将写入 N≥2，两边来源都含「京东精选」，WB 草稿箱至少 +1（同江），Ozon 草稿箱至少 +1（Minjin）</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4074,12 +4074,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>勾选商品，点「采集到草稿箱」，先勾 Wildberries，再勾至少 2 个具体店铺后点「完成」</t>
+          <t>勾选商品，点「采集到草稿箱」，先勾 Wildberries，再勾同江和 Minjin后点「完成」</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>只勾平台不算选完；将写入 N≥2；WB 草稿箱条数至少 +N，且能看到 1688 或 offer</t>
+          <t>只勾平台不算选完；将写入 N≥2；WB 草稿箱至少 +1（同江），Ozon 草稿箱至少 +1（Minjin），且能看到 1688 或 offer</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>勾选后先勾 Ozon，再勾至少 2 个具体 Ozon 店铺，点「完成」</t>
+          <t>勾选后先勾 Ozon，再勾同江和 Minjin，点「完成」</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>只勾平台不算选完；将写入 N≥2；Ozon 草稿箱来源含「京东精选」</t>
+          <t>只勾平台不算选完；将写入 N≥2；WB 草稿箱至少 +1（同江），Ozon 草稿箱至少 +1（Minjin），两边来源都含「京东精选」</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>提示先勾选，不生成草稿</t>
+          <t>提示「请先勾选」，不勾店铺、不点完成，不生成草稿</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -5966,12 +5966,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>先勾 Ozon，再勾至少 2 个具体店铺后点「完成」</t>
+          <t>先勾 Ozon，再勾同江和 Minjin后点「完成」</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>只勾平台不算选完；将写入 N≥2；Ozon 草稿箱来源含「1688精选」</t>
+          <t>只勾平台不算选完；将写入 N≥2；WB 草稿箱至少 +1（同江），Ozon 草稿箱至少 +1（Minjin），两边来源都含「1688精选」</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>先勾 Ozon，再勾至少 2 个具体店铺后点「完成」</t>
+          <t>先勾 Ozon，再勾同江和 Minjin后点「完成」</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>只勾平台不算选完；将写入 N≥2；Ozon 草稿箱来源含「淘宝精选」</t>
+          <t>只勾平台不算选完；将写入 N≥2；WB 草稿箱至少 +1（同江），Ozon 草稿箱至少 +1（Minjin），两边来源都含「淘宝精选」</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>先关闭店铺弹窗，再勾至少 2 个具体 Ozon 店铺后点「完成」</t>
+          <t>先关闭店铺弹窗，再勾同江和 Minjin后点「完成」</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>只勾平台不算选完；关闭后条数不变；完成后将写入 N≥2，来源含「京东精选」且条数至少 +N</t>
+          <t>只勾平台不算选完；关闭后 WB 和 Ozon 草稿箱条数都不变；完成后将写入 N≥2，两边来源都含「京东精选」，WB 草稿箱至少 +1（同江），Ozon 草稿箱至少 +1（Minjin）</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>勾选商品，采集到草稿箱时先勾 Ozon，再勾至少 2 个具体店铺后点「完成」</t>
+          <t>勾选商品，采集到草稿箱时先勾 Ozon，再勾同江和 Minjin后点「完成」</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>只勾平台不算选完；将写入 N≥2；Ozon 草稿箱条数至少 +N，且能看到 offer 或 Ozon</t>
+          <t>只勾平台不算选完；将写入 N≥2；WB 草稿箱至少 +1（同江），Ozon 草稿箱至少 +1（Minjin），且能看到 offer 或 Ozon</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">

--- a/erp_WB_test.xlsx
+++ b/erp_WB_test.xlsx
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>提示「请先勾选」，不勾店铺、不点完成，不生成草稿</t>
+          <t>提示「请先选择目标平台和店铺」或「请先勾选」，不勾店铺、不点完成，不生成草稿</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>京东精选同类提示为「请先勾选京东精选商品」</t>
+          <t>1688实测提示为「请先选择目标平台和店铺」</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>提示「请先勾选京东精选商品」，不勾店铺、不点完成，不生成草稿</t>
+          <t>提示「请先选择目标平台和店铺」或「请先勾选」，不勾店铺、不点完成，不生成草稿</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>实测已出现该提示</t>
+          <t>旧文案「请先勾选京东精选商品」仍算命中</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>提示「请先勾选」，不勾店铺、不点完成，不生成草稿</t>
+          <t>提示「请先选择目标平台和店铺」或「请先勾选」，不勾店铺、不点完成，不生成草稿</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>提示「请先勾选」，不勾店铺、不点完成，不生成草稿</t>
+          <t>提示「请先选择目标平台和店铺」或「请先勾选」，不勾店铺、不点完成，不生成草稿</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
